--- a/data/output/sim_gridrnd/REL1/group_520_60/results/REL1_G9_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_520_60/results/REL1_G9_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G9_521_58_REL1</t>
+          <t>S01_G9_518_59_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>87.47220163083766</v>
       </c>
       <c r="D2" t="n">
-        <v>85.9896219421794</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>476.8248634272251</v>
-      </c>
-      <c r="J2" t="n">
-        <v>73.92487383264108</v>
-      </c>
-      <c r="K2" t="n">
-        <v>496.0487219744577</v>
-      </c>
-      <c r="L2" t="n">
-        <v>63.82849672925573</v>
-      </c>
-      <c r="M2" t="n">
-        <v>489.7484697984092</v>
-      </c>
-      <c r="N2" t="n">
-        <v>61.24557645537098</v>
-      </c>
-      <c r="O2" t="n">
-        <v>495.698226612482</v>
-      </c>
-      <c r="P2" t="n">
-        <v>58.24656960769017</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>494.8248013149671</v>
-      </c>
       <c r="R2" t="n">
-        <v>70.88335020093355</v>
+        <v>549.09</v>
       </c>
       <c r="S2" t="n">
-        <v>499.7415247175116</v>
+        <v>85.61</v>
       </c>
       <c r="T2" t="n">
-        <v>83.39917939642066</v>
+        <v>546.8099999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>497.5235349087177</v>
+        <v>84.25</v>
       </c>
       <c r="V2" t="n">
-        <v>79.26412218698852</v>
+        <v>537.16</v>
       </c>
       <c r="W2" t="n">
-        <v>499.7669605307464</v>
+        <v>76.55</v>
       </c>
       <c r="X2" t="n">
-        <v>76.95681638719823</v>
+        <v>527.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>501.7607107735494</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.36635204697581</v>
+        <v>525.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>73.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>528.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>529.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>524.71</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>75.69</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>524.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>72.66</v>
       </c>
       <c r="AJ2" t="n">
-        <v>504.6</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>502.8</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>502.5</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>502.11</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>500.2166666666666</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>500.05625</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>499.95</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>82.13823713715799</v>
+        <v>495.525</v>
       </c>
       <c r="AT2" t="n">
-        <v>78.36023651487191</v>
+        <v>497.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>74.2398141161466</v>
+        <v>497.3875</v>
       </c>
       <c r="AV2" t="n">
-        <v>68.07068311688961</v>
+        <v>497.48</v>
       </c>
       <c r="AW2" t="n">
-        <v>67.40650108772068</v>
+        <v>497.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>80.68722681706548</v>
+        <v>499.6642857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>89.53485682089126</v>
+        <v>499.475</v>
       </c>
       <c r="AZ2" t="n">
-        <v>93.56639205517236</v>
+        <v>501.3722222222222</v>
       </c>
       <c r="BA2" t="n">
-        <v>93.94450489517735</v>
+        <v>501.235</v>
       </c>
       <c r="BB2" t="n">
-        <v>394</v>
+        <v>99.53993859250667</v>
       </c>
       <c r="BC2" t="n">
-        <v>394</v>
+        <v>97.75825625831645</v>
       </c>
       <c r="BD2" t="n">
-        <v>394</v>
+        <v>92.29334940151431</v>
       </c>
       <c r="BE2" t="n">
-        <v>394</v>
+        <v>85.56172976278589</v>
       </c>
       <c r="BF2" t="n">
-        <v>388</v>
+        <v>78.87063247284547</v>
       </c>
       <c r="BG2" t="n">
-        <v>348</v>
+        <v>82.41156391761376</v>
       </c>
       <c r="BH2" t="n">
-        <v>348</v>
+        <v>84.96006046961125</v>
       </c>
       <c r="BI2" t="n">
-        <v>348</v>
+        <v>87.92541223835093</v>
       </c>
       <c r="BJ2" t="n">
-        <v>348</v>
+        <v>85.80151382697161</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>362</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>362</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>362</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>362</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>362</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>349</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>345</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.6153846153846154</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.9444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="CK2" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.6923076923076923</v>
+      <c r="CL2" t="n">
+        <v>524.67</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>72.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G9_518_59_REL1</t>
+          <t>S02_G9_521_58_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>85.9896219421794</v>
       </c>
       <c r="D3" t="n">
-        <v>87.47220163083766</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>549.0885546320524</v>
-      </c>
-      <c r="J3" t="n">
-        <v>85.60825927524333</v>
-      </c>
-      <c r="K3" t="n">
-        <v>546.8073820819709</v>
-      </c>
-      <c r="L3" t="n">
-        <v>84.24915202900189</v>
-      </c>
-      <c r="M3" t="n">
-        <v>537.1645201731575</v>
-      </c>
-      <c r="N3" t="n">
-        <v>76.54662187182946</v>
-      </c>
-      <c r="O3" t="n">
-        <v>527.0392780183905</v>
-      </c>
-      <c r="P3" t="n">
-        <v>78.68272152096122</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>525.6639225998539</v>
-      </c>
       <c r="R3" t="n">
-        <v>73.6425060825248</v>
+        <v>476.82</v>
       </c>
       <c r="S3" t="n">
-        <v>528.4954759680237</v>
+        <v>73.92</v>
       </c>
       <c r="T3" t="n">
-        <v>72.81892648834753</v>
+        <v>496.05</v>
       </c>
       <c r="U3" t="n">
-        <v>529.3831870823916</v>
+        <v>63.83</v>
       </c>
       <c r="V3" t="n">
-        <v>73.51404275613864</v>
+        <v>489.75</v>
       </c>
       <c r="W3" t="n">
-        <v>524.7074165122557</v>
+        <v>61.25</v>
       </c>
       <c r="X3" t="n">
-        <v>75.69051145279178</v>
+        <v>495.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>524.6666836960128</v>
+        <v>58.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>72.65820584261655</v>
+        <v>494.82</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>70.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>499.74</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>497.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>499.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>501.76</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>74.37</v>
       </c>
       <c r="AJ3" t="n">
-        <v>495.525</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>497.3</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>497.3875</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>497.48</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>497.7</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>499.6642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>499.475</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>501.3722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>501.235</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>99.53993859250667</v>
+        <v>504.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>97.75825625831645</v>
+        <v>502.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>92.29334940151431</v>
+        <v>502.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>85.56172976278589</v>
+        <v>502.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>78.87063247284547</v>
+        <v>500.2166666666666</v>
       </c>
       <c r="AX3" t="n">
-        <v>82.41156391761376</v>
+        <v>500</v>
       </c>
       <c r="AY3" t="n">
-        <v>84.96006046961125</v>
+        <v>500.05625</v>
       </c>
       <c r="AZ3" t="n">
-        <v>87.92541223835093</v>
+        <v>499.95</v>
       </c>
       <c r="BA3" t="n">
-        <v>85.80151382697161</v>
+        <v>500</v>
       </c>
       <c r="BB3" t="n">
-        <v>362</v>
+        <v>82.13823713715799</v>
       </c>
       <c r="BC3" t="n">
-        <v>362</v>
+        <v>78.36023651487191</v>
       </c>
       <c r="BD3" t="n">
-        <v>362</v>
+        <v>74.2398141161466</v>
       </c>
       <c r="BE3" t="n">
-        <v>362</v>
+        <v>68.07068311688961</v>
       </c>
       <c r="BF3" t="n">
-        <v>362</v>
+        <v>67.40650108772068</v>
       </c>
       <c r="BG3" t="n">
-        <v>349</v>
+        <v>80.68722681706548</v>
       </c>
       <c r="BH3" t="n">
-        <v>345</v>
+        <v>89.53485682089126</v>
       </c>
       <c r="BI3" t="n">
-        <v>345</v>
+        <v>93.56639205517236</v>
       </c>
       <c r="BJ3" t="n">
-        <v>345</v>
+        <v>93.94450489517735</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>394</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>388</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>348</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>348</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>348</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>348</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.6956521739130435</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.5384615384615384</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.5769230769230769</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="CE3" t="n">
         <v>0.7692307692307693</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>501.76</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>74.37</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>520</v>
       </c>
       <c r="C4" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D4" t="n">
         <v>59</v>
-      </c>
-      <c r="D4" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E4" t="n">
         <v>520</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>491.670171019052</v>
-      </c>
-      <c r="J4" t="n">
-        <v>42.61054047412836</v>
-      </c>
-      <c r="K4" t="n">
-        <v>519.0236062594587</v>
-      </c>
-      <c r="L4" t="n">
-        <v>48.2558190339909</v>
-      </c>
-      <c r="M4" t="n">
-        <v>528.4758841448403</v>
-      </c>
-      <c r="N4" t="n">
-        <v>59.25337720675967</v>
-      </c>
-      <c r="O4" t="n">
-        <v>519.9868398693444</v>
-      </c>
-      <c r="P4" t="n">
-        <v>60.98472586809186</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>530.5984742211677</v>
-      </c>
       <c r="R4" t="n">
-        <v>60.94048938141061</v>
+        <v>491.67</v>
       </c>
       <c r="S4" t="n">
-        <v>529.6367432110055</v>
+        <v>42.61</v>
       </c>
       <c r="T4" t="n">
-        <v>61.74770771587966</v>
+        <v>519.02</v>
       </c>
       <c r="U4" t="n">
-        <v>533.6264115785815</v>
+        <v>48.26</v>
       </c>
       <c r="V4" t="n">
-        <v>60.83491003148566</v>
+        <v>528.48</v>
       </c>
       <c r="W4" t="n">
-        <v>532.8953427983992</v>
+        <v>59.25</v>
       </c>
       <c r="X4" t="n">
-        <v>59.71682490760429</v>
+        <v>519.99</v>
       </c>
       <c r="Y4" t="n">
-        <v>534.208548850487</v>
+        <v>60.98</v>
       </c>
       <c r="Z4" t="n">
-        <v>60.6185362240682</v>
+        <v>530.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>60.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>529.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>533.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>60.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>532.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>59.72</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>534.21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>60.62</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>507.275</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>503.7166666666666</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>499.975</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>502.59</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>501.4833333333333</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>501.2428571428571</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>499.85625</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>499.5666666666667</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>499.63</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>71.392222090365</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>65.52915169771559</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>71.44770377695843</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>72.22480114199</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>72.24910418514236</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>75.93360553127707</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>74.90676261818754</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>74.55729340580973</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>74.27585812361914</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>386</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>386</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>386</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>386</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>386</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>384</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>384</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>384</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>384</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.1875</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>1</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>1</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.9523809523809523</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>534.21</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>60.62</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>521</v>
       </c>
       <c r="C5" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D5" t="n">
         <v>59</v>
-      </c>
-      <c r="D5" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E5" t="n">
         <v>521</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>540.1881632696084</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41.15613103123215</v>
-      </c>
-      <c r="K5" t="n">
-        <v>536.6066155050825</v>
-      </c>
-      <c r="L5" t="n">
-        <v>46.87984594695492</v>
-      </c>
-      <c r="M5" t="n">
-        <v>541.9467149909377</v>
-      </c>
-      <c r="N5" t="n">
-        <v>49.74636208364143</v>
-      </c>
-      <c r="O5" t="n">
-        <v>534.9807678254119</v>
-      </c>
-      <c r="P5" t="n">
-        <v>44.24179079222069</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>535.823291925829</v>
-      </c>
       <c r="R5" t="n">
-        <v>43.50916150333914</v>
+        <v>540.1900000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>536.4428807147956</v>
+        <v>41.16</v>
       </c>
       <c r="T5" t="n">
-        <v>41.97303248783427</v>
+        <v>536.61</v>
       </c>
       <c r="U5" t="n">
-        <v>535.0839123876277</v>
+        <v>46.88</v>
       </c>
       <c r="V5" t="n">
-        <v>44.8169458788804</v>
+        <v>541.95</v>
       </c>
       <c r="W5" t="n">
-        <v>539.5299970566617</v>
+        <v>49.75</v>
       </c>
       <c r="X5" t="n">
-        <v>52.36061963981653</v>
+        <v>534.98</v>
       </c>
       <c r="Y5" t="n">
-        <v>538.2520650904199</v>
+        <v>44.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>49.57670970339668</v>
+        <v>535.8200000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>43.51</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>536.4400000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>41.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>535.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>44.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>539.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>52.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>538.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>49.58</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>495.075</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>497.85</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>497.575</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>497.36</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>498.1</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>498.4357142857143</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>497.88125</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>498.3666666666667</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>498.515</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>70.90535505164614</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>68.2382651694292</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>65.29965064990778</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>63.88623012825221</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>60.96206470694158</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>59.64660338961782</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>58.30291286408853</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>61.12963456640504</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>65.36665644654008</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>334</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>334</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>334</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>334</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>334</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>334</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>334</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>334</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>334</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>588</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BU5" t="n">
         <v>588</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BV5" t="n">
         <v>588</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BW5" t="n">
         <v>588</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BX5" t="n">
         <v>588</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BY5" t="n">
         <v>588</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BZ5" t="n">
         <v>588</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="CA5" t="n">
         <v>597</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="CB5" t="n">
         <v>601</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="CC5" t="n">
         <v>0.25</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.8235294117647058</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.95</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.84</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.7307692307692307</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>538.25</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>49.58</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>522</v>
       </c>
       <c r="C6" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D6" t="n">
         <v>60</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E6" t="n">
         <v>522</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>530.5572793465508</v>
-      </c>
-      <c r="J6" t="n">
-        <v>40.81327050722593</v>
-      </c>
-      <c r="K6" t="n">
-        <v>535.852436220457</v>
-      </c>
-      <c r="L6" t="n">
-        <v>50.7890104492133</v>
-      </c>
-      <c r="M6" t="n">
-        <v>541.1786278893803</v>
-      </c>
-      <c r="N6" t="n">
-        <v>67.81582293267532</v>
-      </c>
-      <c r="O6" t="n">
-        <v>536.7881115267544</v>
-      </c>
-      <c r="P6" t="n">
-        <v>71.16778469035097</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>523.4950160310549</v>
-      </c>
       <c r="R6" t="n">
-        <v>72.40125571666434</v>
+        <v>530.5599999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>524.0159098230673</v>
+        <v>40.81</v>
       </c>
       <c r="T6" t="n">
-        <v>70.62303744130233</v>
+        <v>535.85</v>
       </c>
       <c r="U6" t="n">
-        <v>522.3453048185473</v>
+        <v>50.79</v>
       </c>
       <c r="V6" t="n">
-        <v>69.40556070678198</v>
+        <v>541.1799999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>521.8732727634185</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>66.48793261920933</v>
+        <v>536.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>519.0910705126141</v>
+        <v>71.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>65.40833435205241</v>
+        <v>523.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>524.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>70.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>522.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>69.41</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>521.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>519.09</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>65.41</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>498.075</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>499.05</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>498.4375</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>497.99</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>500.8666666666667</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>501.8571428571428</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>503.30625</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>502.85</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>500.02</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>75.31712537663661</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>68.76613144079965</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>83.63534595940881</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>95.15550378196733</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>93.45845185012548</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>92.70102260405078</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>90.3187409175831</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>85.41756747492482</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>82.83332421193779</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>336</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>336</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>336</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>336</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>336</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>336</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>336</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>336</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>336</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BT6" t="n">
         <v>636</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BU6" t="n">
         <v>636</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BV6" t="n">
         <v>636</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BW6" t="n">
         <v>636</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BX6" t="n">
         <v>636</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BY6" t="n">
         <v>636</v>
       </c>
-      <c r="BQ6" t="n">
+      <c r="BZ6" t="n">
         <v>636</v>
       </c>
-      <c r="BR6" t="n">
+      <c r="CA6" t="n">
         <v>636</v>
       </c>
-      <c r="BS6" t="n">
+      <c r="CB6" t="n">
         <v>636</v>
       </c>
-      <c r="BT6" t="n">
+      <c r="CC6" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>1</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>1</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.8888888888888888</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>519.09</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>65.41</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>520</v>
       </c>
       <c r="C7" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D7" t="n">
         <v>62</v>
-      </c>
-      <c r="D7" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E7" t="n">
         <v>520</v>
@@ -2082,720 +2302,819 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>509.4273658408023</v>
-      </c>
-      <c r="J7" t="n">
-        <v>68.52786079598076</v>
-      </c>
-      <c r="K7" t="n">
-        <v>504.8653754951773</v>
-      </c>
-      <c r="L7" t="n">
-        <v>65.14713322360835</v>
-      </c>
-      <c r="M7" t="n">
-        <v>511.1234321279848</v>
-      </c>
-      <c r="N7" t="n">
-        <v>71.26278337707774</v>
-      </c>
-      <c r="O7" t="n">
-        <v>519.0927256753323</v>
-      </c>
-      <c r="P7" t="n">
-        <v>76.43613431462909</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>519.9957337820922</v>
-      </c>
       <c r="R7" t="n">
-        <v>79.10098820469916</v>
+        <v>509.43</v>
       </c>
       <c r="S7" t="n">
-        <v>515.5131151068364</v>
+        <v>68.53</v>
       </c>
       <c r="T7" t="n">
-        <v>81.51773868081483</v>
+        <v>504.87</v>
       </c>
       <c r="U7" t="n">
-        <v>507.6845268952063</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>76.82612093084379</v>
+        <v>511.12</v>
       </c>
       <c r="W7" t="n">
-        <v>507.480074488324</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>75.63481612431339</v>
+        <v>519.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>509.4852899379357</v>
+        <v>76.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>78.22514983184961</v>
+        <v>520</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>515.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>81.52</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>507.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>76.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>507.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>75.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>509.49</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>78.23</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>497.025</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>497.7166666666666</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>496.975</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>497.02</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>498.0166666666667</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>499.15</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>500.70625</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>499.5777777777778</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>500.415</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>108.7879790004392</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>96.36996275926553</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>90.41362936526771</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>88.07178662886317</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>90.32210723602255</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>90.1428964795024</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>86.11762282446898</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>83.7369529177568</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>85.95366644303196</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>342</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>342</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>342</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>342</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>342</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>342</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>342</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>342</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>342</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>1</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.7391304347826086</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>509.49</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>78.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G9_518_61_REL1</t>
+          <t>S07_G9_521_62_REL1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>91.91994069681246</v>
       </c>
       <c r="D8" t="n">
-        <v>90.43736100815418</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>482.6594542121456</v>
-      </c>
-      <c r="J8" t="n">
-        <v>89.8622345677209</v>
-      </c>
-      <c r="K8" t="n">
-        <v>507.1795678458899</v>
-      </c>
-      <c r="L8" t="n">
-        <v>84.43117115866129</v>
-      </c>
-      <c r="M8" t="n">
-        <v>515.5707791130079</v>
-      </c>
-      <c r="N8" t="n">
-        <v>78.70996437442309</v>
-      </c>
-      <c r="O8" t="n">
-        <v>502.8220640995926</v>
-      </c>
-      <c r="P8" t="n">
-        <v>77.53346805932649</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>513.1232471064349</v>
-      </c>
       <c r="R8" t="n">
-        <v>74.06430421688559</v>
+        <v>511.77</v>
       </c>
       <c r="S8" t="n">
-        <v>508.2928765475841</v>
+        <v>42.53</v>
       </c>
       <c r="T8" t="n">
-        <v>75.44637410424939</v>
+        <v>512.25</v>
       </c>
       <c r="U8" t="n">
-        <v>503.2003530538933</v>
+        <v>60.21</v>
       </c>
       <c r="V8" t="n">
-        <v>69.30642822065286</v>
+        <v>518.55</v>
       </c>
       <c r="W8" t="n">
-        <v>504.3618703193904</v>
+        <v>51.22</v>
       </c>
       <c r="X8" t="n">
-        <v>70.37465162583403</v>
+        <v>520.3099999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>499.558259570623</v>
+        <v>49.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.25608117876953</v>
+        <v>510.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>53.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>514.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>53.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>515.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>60.78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>514.6900000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>67.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>509.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>70.91</v>
       </c>
       <c r="AJ8" t="n">
-        <v>498.4</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>498.3</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>498.8625</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>498.63</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>497.65</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>498.0428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>498.80625</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>498.55</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>499.48</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>138.6978370415343</v>
+        <v>496.075</v>
       </c>
       <c r="AT8" t="n">
-        <v>122.0679182531867</v>
+        <v>497.2333333333333</v>
       </c>
       <c r="AU8" t="n">
-        <v>109.5408307150808</v>
+        <v>497.8625</v>
       </c>
       <c r="AV8" t="n">
-        <v>105.1194230387515</v>
+        <v>498.54</v>
       </c>
       <c r="AW8" t="n">
-        <v>99.24696888738383</v>
+        <v>499.05</v>
       </c>
       <c r="AX8" t="n">
-        <v>95.89189384991022</v>
+        <v>499.0214285714285</v>
       </c>
       <c r="AY8" t="n">
-        <v>94.71341621405861</v>
+        <v>499.31875</v>
       </c>
       <c r="AZ8" t="n">
-        <v>92.61307053182793</v>
+        <v>499.3277777777778</v>
       </c>
       <c r="BA8" t="n">
-        <v>90.51375365103361</v>
+        <v>499.535</v>
       </c>
       <c r="BB8" t="n">
-        <v>290</v>
+        <v>71.71310462530542</v>
       </c>
       <c r="BC8" t="n">
-        <v>290</v>
+        <v>68.79422617891386</v>
       </c>
       <c r="BD8" t="n">
-        <v>290</v>
+        <v>65.85794252593988</v>
       </c>
       <c r="BE8" t="n">
-        <v>290</v>
+        <v>67.5673619434709</v>
       </c>
       <c r="BF8" t="n">
-        <v>290</v>
+        <v>64.98305548371822</v>
       </c>
       <c r="BG8" t="n">
-        <v>290</v>
+        <v>64.77559812340522</v>
       </c>
       <c r="BH8" t="n">
-        <v>290</v>
+        <v>66.05399040510346</v>
       </c>
       <c r="BI8" t="n">
-        <v>290</v>
+        <v>72.21679018033561</v>
       </c>
       <c r="BJ8" t="n">
-        <v>290</v>
+        <v>77.6813283550172</v>
       </c>
       <c r="BK8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BL8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BM8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BN8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BO8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BP8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BQ8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BR8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BS8" t="n">
-        <v>696</v>
+        <v>330</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.4166666666666667</v>
+        <v>637</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.75</v>
+        <v>637</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.8461538461538461</v>
+        <v>637</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.9333333333333333</v>
+        <v>637</v>
       </c>
       <c r="BY8" t="n">
-        <v>1</v>
+        <v>637</v>
       </c>
       <c r="BZ8" t="n">
+        <v>637</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>637</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>637</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CH8" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="CA8" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.6666666666666666</v>
+      <c r="CI8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>509.42</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>70.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S07_G9_521_62_REL1</t>
+          <t>S08_G9_518_61_REL1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>90.43736100815418</v>
       </c>
       <c r="D9" t="n">
-        <v>91.91994069681246</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>511.7721968849644</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42.52794263897526</v>
-      </c>
-      <c r="K9" t="n">
-        <v>512.2469155130686</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60.20562777214164</v>
-      </c>
-      <c r="M9" t="n">
-        <v>518.5488547151107</v>
-      </c>
-      <c r="N9" t="n">
-        <v>51.22456338761218</v>
-      </c>
-      <c r="O9" t="n">
-        <v>520.3057476548088</v>
-      </c>
-      <c r="P9" t="n">
-        <v>49.42539178493718</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>510.2945846276493</v>
-      </c>
       <c r="R9" t="n">
-        <v>53.13152359665852</v>
+        <v>482.66</v>
       </c>
       <c r="S9" t="n">
-        <v>514.2410546269933</v>
+        <v>89.86</v>
       </c>
       <c r="T9" t="n">
-        <v>53.21522564031027</v>
+        <v>507.18</v>
       </c>
       <c r="U9" t="n">
-        <v>515.1029375072154</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>60.78145840514706</v>
+        <v>515.5700000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>514.6863403846023</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>67.22708006629921</v>
+        <v>502.82</v>
       </c>
       <c r="Y9" t="n">
-        <v>509.421862202276</v>
+        <v>77.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>70.90731006298796</v>
+        <v>513.12</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>74.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>508.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>75.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>503.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>69.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>504.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>70.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>499.56</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>496.075</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>497.2333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>497.8625</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>498.54</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>499.05</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>499.0214285714285</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>499.31875</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>499.3277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>499.535</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>71.71310462530542</v>
+        <v>498.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>68.79422617891386</v>
+        <v>498.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>65.85794252593988</v>
+        <v>498.8625</v>
       </c>
       <c r="AV9" t="n">
-        <v>67.5673619434709</v>
+        <v>498.63</v>
       </c>
       <c r="AW9" t="n">
-        <v>64.98305548371822</v>
+        <v>497.65</v>
       </c>
       <c r="AX9" t="n">
-        <v>64.77559812340522</v>
+        <v>498.0428571428571</v>
       </c>
       <c r="AY9" t="n">
-        <v>66.05399040510346</v>
+        <v>498.80625</v>
       </c>
       <c r="AZ9" t="n">
-        <v>72.21679018033561</v>
+        <v>498.55</v>
       </c>
       <c r="BA9" t="n">
-        <v>77.6813283550172</v>
+        <v>499.48</v>
       </c>
       <c r="BB9" t="n">
-        <v>330</v>
+        <v>138.6978370415343</v>
       </c>
       <c r="BC9" t="n">
-        <v>330</v>
+        <v>122.0679182531867</v>
       </c>
       <c r="BD9" t="n">
-        <v>330</v>
+        <v>109.5408307150808</v>
       </c>
       <c r="BE9" t="n">
-        <v>330</v>
+        <v>105.1194230387515</v>
       </c>
       <c r="BF9" t="n">
-        <v>330</v>
+        <v>99.24696888738383</v>
       </c>
       <c r="BG9" t="n">
-        <v>330</v>
+        <v>95.89189384991022</v>
       </c>
       <c r="BH9" t="n">
-        <v>330</v>
+        <v>94.71341621405861</v>
       </c>
       <c r="BI9" t="n">
-        <v>330</v>
+        <v>92.61307053182793</v>
       </c>
       <c r="BJ9" t="n">
-        <v>330</v>
+        <v>90.51375365103361</v>
       </c>
       <c r="BK9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BL9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BM9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BN9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BO9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BP9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BQ9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BR9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BS9" t="n">
-        <v>637</v>
+        <v>290</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.8</v>
+        <v>696</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.8125</v>
+        <v>696</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.7647058823529411</v>
+        <v>696</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.7222222222222222</v>
+        <v>696</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.7222222222222222</v>
+        <v>696</v>
       </c>
       <c r="BY9" t="n">
+        <v>696</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>696</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>696</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>696</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI9" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.9</v>
+      <c r="CJ9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>499.56</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>520</v>
       </c>
       <c r="C10" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D10" t="n">
         <v>62</v>
-      </c>
-      <c r="D10" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E10" t="n">
         <v>520</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>507.3009918499572</v>
-      </c>
-      <c r="J10" t="n">
-        <v>73.69372934207635</v>
-      </c>
-      <c r="K10" t="n">
-        <v>492.5142737778377</v>
-      </c>
-      <c r="L10" t="n">
-        <v>99.77779371432516</v>
-      </c>
-      <c r="M10" t="n">
-        <v>514.6831231281576</v>
-      </c>
-      <c r="N10" t="n">
-        <v>94.94331619567878</v>
-      </c>
-      <c r="O10" t="n">
-        <v>520.3209156558933</v>
-      </c>
-      <c r="P10" t="n">
-        <v>92.39253139890572</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>520.3835259201612</v>
-      </c>
       <c r="R10" t="n">
-        <v>87.47392644000956</v>
+        <v>507.3</v>
       </c>
       <c r="S10" t="n">
-        <v>520.8693298821353</v>
+        <v>73.69</v>
       </c>
       <c r="T10" t="n">
-        <v>85.0959400312735</v>
+        <v>492.51</v>
       </c>
       <c r="U10" t="n">
-        <v>526.9796371402755</v>
+        <v>99.78</v>
       </c>
       <c r="V10" t="n">
-        <v>85.15443833821892</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>532.4811660514837</v>
+        <v>94.94</v>
       </c>
       <c r="X10" t="n">
-        <v>88.2011639684624</v>
+        <v>520.3200000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>525.087872284714</v>
+        <v>92.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>88.68673343405712</v>
+        <v>520.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>87.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>520.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>526.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>532.48</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>525.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>88.69</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>499.475</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>499.7833333333334</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>499.475</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>499.59</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>500.25</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>498.6857142857143</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>498.5125</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>498.5055555555555</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>498.085</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>78.36452880608675</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>90.56399057511152</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>93.78658952643495</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>97.56270752700541</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>95.28048506033821</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>92.46073187453963</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>90.25706256991749</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>98.56309300376655</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>101.3500753576434</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>361</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>361</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>361</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>360</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>360</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>355</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>355</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>334</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>331</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.9444444444444444</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>1</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>1</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.9</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.8571428571428571</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>525.09</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>88.69</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>518</v>
       </c>
       <c r="C11" t="n">
+        <v>91.91994069681246</v>
+      </c>
+      <c r="D11" t="n">
         <v>62</v>
-      </c>
-      <c r="D11" t="n">
-        <v>91.91994069681246</v>
       </c>
       <c r="E11" t="n">
         <v>518</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>525.1008859343465</v>
-      </c>
-      <c r="J11" t="n">
-        <v>115.3641691521929</v>
-      </c>
-      <c r="K11" t="n">
-        <v>538.6187363152417</v>
-      </c>
-      <c r="L11" t="n">
-        <v>92.11199249076769</v>
-      </c>
-      <c r="M11" t="n">
-        <v>551.5776914945562</v>
-      </c>
-      <c r="N11" t="n">
-        <v>102.8528378121942</v>
-      </c>
-      <c r="O11" t="n">
-        <v>554.3938898438574</v>
-      </c>
-      <c r="P11" t="n">
-        <v>94.62876566541044</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>537.7229092119378</v>
-      </c>
       <c r="R11" t="n">
-        <v>95.90986390264183</v>
+        <v>525.1</v>
       </c>
       <c r="S11" t="n">
-        <v>526.5274282652211</v>
+        <v>115.36</v>
       </c>
       <c r="T11" t="n">
-        <v>101.300605000267</v>
+        <v>538.62</v>
       </c>
       <c r="U11" t="n">
-        <v>523.7038831944652</v>
+        <v>92.11</v>
       </c>
       <c r="V11" t="n">
-        <v>98.25358209340889</v>
+        <v>551.58</v>
       </c>
       <c r="W11" t="n">
-        <v>528.543886574054</v>
+        <v>102.85</v>
       </c>
       <c r="X11" t="n">
-        <v>91.98466144475289</v>
+        <v>554.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>525.4914033089865</v>
+        <v>94.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>86.94907880599797</v>
+        <v>537.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>95.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>526.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>101.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>523.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>98.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>528.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>91.98</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>525.49</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>86.95</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>495.175</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>495.8166666666667</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>495.8625</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>495.52</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>495.675</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>496.1928571428571</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>497.28125</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>498</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>498.455</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>133.7519883029781</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>119.5474092381577</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>115.0043198916893</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>116.0071101269228</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>108.2496468431499</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>110.458712159054</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>110.7674462486046</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>109.4686154921938</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>108.2746876005652</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>280</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>280</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>280</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>280</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>280</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>280</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>280</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>280</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>280</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>675</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>675</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>675</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>675</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>675</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>675</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>675</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>675</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>675</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.6</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.78125</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>525.49</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>86.95</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>518</v>
       </c>
       <c r="C12" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D12" t="n">
         <v>60</v>
-      </c>
-      <c r="D12" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E12" t="n">
         <v>518</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>527.9267020991286</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33.90831764999408</v>
-      </c>
-      <c r="K12" t="n">
-        <v>531.9133227642249</v>
-      </c>
-      <c r="L12" t="n">
-        <v>29.94805454083815</v>
-      </c>
-      <c r="M12" t="n">
-        <v>527.9777020599973</v>
-      </c>
-      <c r="N12" t="n">
-        <v>40.37020919633328</v>
-      </c>
-      <c r="O12" t="n">
-        <v>520.8702218816034</v>
-      </c>
-      <c r="P12" t="n">
-        <v>54.03055510118757</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>519.5811782690769</v>
-      </c>
       <c r="R12" t="n">
-        <v>63.65867839472191</v>
+        <v>527.9299999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>516.1353816411826</v>
+        <v>33.91</v>
       </c>
       <c r="T12" t="n">
-        <v>59.08941466575147</v>
+        <v>531.91</v>
       </c>
       <c r="U12" t="n">
-        <v>518.3715679823687</v>
+        <v>29.95</v>
       </c>
       <c r="V12" t="n">
-        <v>58.44116827213967</v>
+        <v>527.98</v>
       </c>
       <c r="W12" t="n">
-        <v>515.3615320691546</v>
+        <v>40.37</v>
       </c>
       <c r="X12" t="n">
-        <v>56.64090140017834</v>
+        <v>520.87</v>
       </c>
       <c r="Y12" t="n">
-        <v>517.0656540847405</v>
+        <v>54.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>57.36532894277592</v>
+        <v>519.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>63.66</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>516.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>59.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>518.37</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>58.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>515.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>56.64</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>517.0700000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>57.37</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>497.95</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>497.8</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>496.95</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>499.19</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>499.0666666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>500.3928571428572</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>499.6625</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>501.1277777777778</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>501.32</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>71.27725794389119</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>63.87873929041911</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>62.05701007944227</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>65.46490586566209</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>73.78388863581414</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>76.19642815293447</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>74.29046771793809</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>71.80622307877992</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>72.50722446763494</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>340</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>340</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>340</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>340</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>340</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>340</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>340</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>340</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>340</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>636</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>636</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>636</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>636</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>636</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>636</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>636</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>636</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>636</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.9565217391304348</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>517.0700000000001</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>57.37</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>521</v>
       </c>
       <c r="C13" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D13" t="n">
         <v>58</v>
-      </c>
-      <c r="D13" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E13" t="n">
         <v>521</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>501.5813032869168</v>
-      </c>
-      <c r="J13" t="n">
-        <v>88.52574478144493</v>
-      </c>
-      <c r="K13" t="n">
-        <v>507.8140357663557</v>
-      </c>
-      <c r="L13" t="n">
-        <v>75.45435941274381</v>
-      </c>
-      <c r="M13" t="n">
-        <v>510.2107213745263</v>
-      </c>
-      <c r="N13" t="n">
-        <v>72.82878656240011</v>
-      </c>
-      <c r="O13" t="n">
-        <v>516.652470668071</v>
-      </c>
-      <c r="P13" t="n">
-        <v>67.91881280397448</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>515.8070297757145</v>
-      </c>
       <c r="R13" t="n">
-        <v>67.65040432503368</v>
+        <v>501.58</v>
       </c>
       <c r="S13" t="n">
-        <v>520.9844578177376</v>
+        <v>88.53</v>
       </c>
       <c r="T13" t="n">
-        <v>67.78710050284074</v>
+        <v>507.81</v>
       </c>
       <c r="U13" t="n">
-        <v>514.3484548198008</v>
+        <v>75.45</v>
       </c>
       <c r="V13" t="n">
-        <v>64.03775056883256</v>
+        <v>510.21</v>
       </c>
       <c r="W13" t="n">
-        <v>514.0066430962847</v>
+        <v>72.83</v>
       </c>
       <c r="X13" t="n">
-        <v>61.15153493673364</v>
+        <v>516.65</v>
       </c>
       <c r="Y13" t="n">
-        <v>509.8302451054506</v>
+        <v>67.92</v>
       </c>
       <c r="Z13" t="n">
-        <v>59.27868672102353</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>520.98</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>514.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>514.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>61.15</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>509.83</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>59.28</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>502.25</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>501.7166666666666</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>501.6375</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>501.16</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>500.6166666666667</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>501.3214285714286</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>499.8</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>498.4444444444445</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>497.53</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>100.643616290354</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>93.33025441350135</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>84.91101868279523</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>77.37218104719553</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>76.4395385618958</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>76.86205341455587</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>75.70896578345263</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>73.87430933854417</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>72.84572121957473</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>378</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>378</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>378</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>378</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>366</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>366</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>366</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>366</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>366</v>
       </c>
-      <c r="BK13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>669</v>
-      </c>
       <c r="BT13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
         <v>0.7857142857142857</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.75</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.5454545454545454</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>509.83</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>59.28</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>518</v>
       </c>
       <c r="C14" t="n">
+        <v>90.43736100815418</v>
+      </c>
+      <c r="D14" t="n">
         <v>61</v>
-      </c>
-      <c r="D14" t="n">
-        <v>90.43736100815418</v>
       </c>
       <c r="E14" t="n">
         <v>518</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>552.2416347982643</v>
-      </c>
-      <c r="J14" t="n">
-        <v>48.28217543065608</v>
-      </c>
-      <c r="K14" t="n">
-        <v>548.5076337152069</v>
-      </c>
-      <c r="L14" t="n">
-        <v>75.65145629341214</v>
-      </c>
-      <c r="M14" t="n">
-        <v>536.9945887684078</v>
-      </c>
-      <c r="N14" t="n">
-        <v>76.59103021448456</v>
-      </c>
-      <c r="O14" t="n">
-        <v>527.2504573722838</v>
-      </c>
-      <c r="P14" t="n">
-        <v>77.83683858661533</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>519.8552941584785</v>
-      </c>
       <c r="R14" t="n">
-        <v>82.27448231058366</v>
+        <v>552.24</v>
       </c>
       <c r="S14" t="n">
-        <v>521.3216074326242</v>
+        <v>48.28</v>
       </c>
       <c r="T14" t="n">
-        <v>84.10616200506689</v>
+        <v>548.51</v>
       </c>
       <c r="U14" t="n">
-        <v>521.1282371874474</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>84.66709528072673</v>
+        <v>536.99</v>
       </c>
       <c r="W14" t="n">
-        <v>514.9575694517098</v>
+        <v>76.59</v>
       </c>
       <c r="X14" t="n">
-        <v>80.39299938792949</v>
+        <v>527.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>517.6905486018838</v>
+        <v>77.84</v>
       </c>
       <c r="Z14" t="n">
-        <v>82.53747340223212</v>
+        <v>519.86</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>82.27</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>521.3200000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>84.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>521.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>84.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>514.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>80.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>517.6900000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>500.775</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>499.1166666666667</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>498.525</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>496.43</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>496.9333333333333</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>498.3785714285714</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>498.25</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>499.1888888888889</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>499.545</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>74.60679845027529</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>88.08066221115482</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>92.13752967710823</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>91.67183373315929</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>92.09394961426921</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>94.01432017495624</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>95.02177382053021</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>94.75675225948508</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>93.71695671008528</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>369</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>352</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>352</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>352</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>352</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>352</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>352</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>352</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>352</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.92</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>517.6900000000001</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="n">
+        <v>88.95478131949592</v>
+      </c>
+      <c r="D15" t="n">
         <v>60</v>
-      </c>
-      <c r="D15" t="n">
-        <v>88.95478131949592</v>
       </c>
       <c r="E15" t="n">
         <v>518</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>491.2338790743784</v>
-      </c>
-      <c r="J15" t="n">
-        <v>77.77615696816842</v>
-      </c>
-      <c r="K15" t="n">
-        <v>513.3907337374869</v>
-      </c>
-      <c r="L15" t="n">
-        <v>97.47723347382707</v>
-      </c>
-      <c r="M15" t="n">
-        <v>528.061939568285</v>
-      </c>
-      <c r="N15" t="n">
-        <v>90.11564111809562</v>
-      </c>
-      <c r="O15" t="n">
-        <v>534.319791669301</v>
-      </c>
-      <c r="P15" t="n">
-        <v>91.68056813208736</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>532.4549664359835</v>
-      </c>
       <c r="R15" t="n">
-        <v>93.74925584597507</v>
+        <v>491.23</v>
       </c>
       <c r="S15" t="n">
-        <v>533.9931139314369</v>
+        <v>77.78</v>
       </c>
       <c r="T15" t="n">
-        <v>92.34841670456736</v>
+        <v>513.39</v>
       </c>
       <c r="U15" t="n">
-        <v>537.3106384806357</v>
+        <v>97.48</v>
       </c>
       <c r="V15" t="n">
-        <v>87.59384673745421</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>532.7697466717037</v>
+        <v>90.12</v>
       </c>
       <c r="X15" t="n">
-        <v>86.8987793515614</v>
+        <v>534.3200000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>530.3898076973736</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>82.74408152672264</v>
+        <v>532.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>93.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>533.99</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>537.3099999999999</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>87.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>532.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>530.39</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>499.375</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>499.9333333333333</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>498.6625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>498.68</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>498.9916666666667</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>499.2285714285715</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>499.13125</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>499.1111111111111</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>499.15</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>82.39711387542648</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>82.8598951376492</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>84.95851101420034</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>85.75393635279957</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>86.59055913063246</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>88.8326953047246</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>91.34352206608578</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>90.58058958671303</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>88.21869133012572</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>334</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>334</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>334</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>334</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>334</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>334</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>334</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>334</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>334</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>637</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>637</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>637</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>637</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>637</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>637</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>637</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>637</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>637</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="BU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV15" t="n">
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.5625</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.6578947368421053</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.8292682926829268</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8536585365853658</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>530.39</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>519</v>
       </c>
       <c r="C16" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D16" t="n">
         <v>58</v>
-      </c>
-      <c r="D16" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E16" t="n">
         <v>519</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>517.4327760546918</v>
-      </c>
-      <c r="J16" t="n">
-        <v>62.05882633125725</v>
-      </c>
-      <c r="K16" t="n">
-        <v>521.5459870734087</v>
-      </c>
-      <c r="L16" t="n">
-        <v>60.78736026972181</v>
-      </c>
-      <c r="M16" t="n">
-        <v>517.4196685183633</v>
-      </c>
-      <c r="N16" t="n">
-        <v>61.33128246097346</v>
-      </c>
-      <c r="O16" t="n">
-        <v>518.1541793796415</v>
-      </c>
-      <c r="P16" t="n">
-        <v>59.64933119088469</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>518.846654942948</v>
-      </c>
       <c r="R16" t="n">
-        <v>57.33249330252647</v>
+        <v>517.4299999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>522.1950190654205</v>
+        <v>62.06</v>
       </c>
       <c r="T16" t="n">
-        <v>58.35755378839094</v>
+        <v>521.55</v>
       </c>
       <c r="U16" t="n">
-        <v>515.4518767676188</v>
+        <v>60.79</v>
       </c>
       <c r="V16" t="n">
-        <v>61.1952796915982</v>
+        <v>517.42</v>
       </c>
       <c r="W16" t="n">
-        <v>516.7761234131359</v>
+        <v>61.33</v>
       </c>
       <c r="X16" t="n">
-        <v>59.74333463277977</v>
+        <v>518.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>519.1521382227328</v>
+        <v>59.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>61.34375104051466</v>
+        <v>518.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>57.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>522.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>58.36</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>515.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>61.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>516.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>59.74</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>519.15</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>61.34</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>494.075</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>495.7833333333334</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>494.875</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>494.23</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>494.375</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>494.9</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>494.71875</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>495.5277777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>495.65</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>72.41007785522675</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>72.09093601525477</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>69.933606906837</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>71.00166969867681</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>69.71573979382275</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>69.7811169709563</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>70.75452033925112</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>69.20929855281615</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>68.80179866834878</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>339</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>339</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>339</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>339</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>339</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>339</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>339</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>339</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>339</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>636</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>636</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>636</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>636</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>636</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>636</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>636</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>636</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>636</v>
       </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
         <v>0.5</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.9</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.8611111111111112</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>519.15</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>61.34</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>518</v>
       </c>
       <c r="C17" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D17" t="n">
         <v>58</v>
-      </c>
-      <c r="D17" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E17" t="n">
         <v>518</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>511.9820617323675</v>
-      </c>
-      <c r="J17" t="n">
-        <v>90.92235240763945</v>
-      </c>
-      <c r="K17" t="n">
-        <v>536.9982948109506</v>
-      </c>
-      <c r="L17" t="n">
-        <v>76.3961883014228</v>
-      </c>
-      <c r="M17" t="n">
-        <v>532.564414611237</v>
-      </c>
-      <c r="N17" t="n">
-        <v>80.10983432413563</v>
-      </c>
-      <c r="O17" t="n">
-        <v>531.2655587985215</v>
-      </c>
-      <c r="P17" t="n">
-        <v>74.11090364808871</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>527.9639591107652</v>
-      </c>
       <c r="R17" t="n">
-        <v>74.21067653256989</v>
+        <v>511.98</v>
       </c>
       <c r="S17" t="n">
-        <v>524.8070015288391</v>
+        <v>90.92</v>
       </c>
       <c r="T17" t="n">
-        <v>75.98982570669136</v>
+        <v>537</v>
       </c>
       <c r="U17" t="n">
-        <v>525.3212486114471</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>75.17482087973852</v>
+        <v>532.5599999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>523.333377562133</v>
+        <v>80.11</v>
       </c>
       <c r="X17" t="n">
-        <v>75.72274423828372</v>
+        <v>531.27</v>
       </c>
       <c r="Y17" t="n">
-        <v>525.983368684221</v>
+        <v>74.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>75.05022897951828</v>
+        <v>527.96</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>524.8099999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>525.3200000000001</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>75.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>523.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>75.72</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>525.98</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>75.05</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>499</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>499.6666666666667</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>500.4875</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>503.21</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>501.8916666666667</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>500.0857142857143</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>501.63125</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>500.3166666666667</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>499.925</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>140.1973608881422</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>119.507554386974</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>112.069174369003</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>105.2251200997176</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>101.7667099983531</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>99.53107811233677</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>97.42417704778161</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>96.22257040609317</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>94.66139326568144</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>288</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>288</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>288</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>288</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>288</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>288</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>288</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>288</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>288</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>735</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>735</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>735</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>735</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>735</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>735</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>735</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>735</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>735</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.625</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>1</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>1</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.9230769230769231</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>525.98</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>75.05</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>520</v>
       </c>
       <c r="C18" t="n">
+        <v>87.47220163083766</v>
+      </c>
+      <c r="D18" t="n">
         <v>59</v>
-      </c>
-      <c r="D18" t="n">
-        <v>87.47220163083766</v>
       </c>
       <c r="E18" t="n">
         <v>520</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>508.5261677485295</v>
-      </c>
-      <c r="J18" t="n">
-        <v>50.59719231106293</v>
-      </c>
-      <c r="K18" t="n">
-        <v>511.4080319091703</v>
-      </c>
-      <c r="L18" t="n">
-        <v>73.23720045206385</v>
-      </c>
-      <c r="M18" t="n">
-        <v>511.6959690219297</v>
-      </c>
-      <c r="N18" t="n">
-        <v>68.854064174218</v>
-      </c>
-      <c r="O18" t="n">
-        <v>507.7188902340115</v>
-      </c>
-      <c r="P18" t="n">
-        <v>78.49581275782491</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>509.3330711625179</v>
-      </c>
       <c r="R18" t="n">
-        <v>79.2357966441302</v>
+        <v>508.53</v>
       </c>
       <c r="S18" t="n">
-        <v>512.6889327840959</v>
+        <v>50.6</v>
       </c>
       <c r="T18" t="n">
-        <v>73.22356458690629</v>
+        <v>511.41</v>
       </c>
       <c r="U18" t="n">
-        <v>519.6364983371921</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>72.80554292060972</v>
+        <v>511.7</v>
       </c>
       <c r="W18" t="n">
-        <v>519.2417679563343</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>71.19153454979556</v>
+        <v>507.72</v>
       </c>
       <c r="Y18" t="n">
-        <v>518.5176464879534</v>
+        <v>78.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>79.86025327859039</v>
+        <v>509.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>512.6900000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>73.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>519.64</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>72.81</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>519.24</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>71.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>518.52</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>79.86</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>502.125</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>501.0333333333334</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>499.0875</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>497.19</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>497.1083333333333</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>497.3285714285714</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>498.05</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>497.9666666666666</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>498.57</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>77.56583896922666</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>77.12867315222155</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>82.3155808079491</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>84.40375524821155</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>88.152594576425</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>86.97770181054969</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>84.61100696717892</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>85.27119482373088</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>86.01717909813132</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>333</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>333</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>333</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>333</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>333</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>333</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>333</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>333</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>333</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BT18" t="n">
         <v>642</v>
       </c>
-      <c r="BL18" t="n">
+      <c r="BU18" t="n">
         <v>642</v>
       </c>
-      <c r="BM18" t="n">
+      <c r="BV18" t="n">
         <v>642</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BW18" t="n">
         <v>642</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BX18" t="n">
         <v>642</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BY18" t="n">
         <v>642</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BZ18" t="n">
         <v>642</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="CA18" t="n">
         <v>642</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="CB18" t="n">
         <v>642</v>
       </c>
-      <c r="BT18" t="n">
+      <c r="CC18" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>1</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>1</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.7894736842105263</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.8076923076923077</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>518.52</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>79.86</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>522</v>
       </c>
       <c r="C19" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D19" t="n">
         <v>58</v>
-      </c>
-      <c r="D19" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E19" t="n">
         <v>522</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>605.2248202382921</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25.88284170311296</v>
-      </c>
-      <c r="K19" t="n">
-        <v>525.171754375311</v>
-      </c>
-      <c r="L19" t="n">
-        <v>84.37112440655271</v>
-      </c>
-      <c r="M19" t="n">
-        <v>522.6835949820763</v>
-      </c>
-      <c r="N19" t="n">
-        <v>96.9352256093016</v>
-      </c>
-      <c r="O19" t="n">
-        <v>529.0491340875924</v>
-      </c>
-      <c r="P19" t="n">
-        <v>85.96738768343353</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>531.5444853092976</v>
-      </c>
       <c r="R19" t="n">
-        <v>81.19505445217385</v>
+        <v>605.22</v>
       </c>
       <c r="S19" t="n">
-        <v>528.5727581766737</v>
+        <v>25.88</v>
       </c>
       <c r="T19" t="n">
-        <v>88.83764821013031</v>
+        <v>525.17</v>
       </c>
       <c r="U19" t="n">
-        <v>523.4948903300245</v>
+        <v>84.37</v>
       </c>
       <c r="V19" t="n">
-        <v>82.76448287964338</v>
+        <v>522.6799999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>524.0351013304139</v>
+        <v>96.94</v>
       </c>
       <c r="X19" t="n">
-        <v>82.65936521738334</v>
+        <v>529.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>517.0018602637069</v>
+        <v>85.97</v>
       </c>
       <c r="Z19" t="n">
-        <v>83.00723803628297</v>
+        <v>531.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>81.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>528.5700000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>88.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>523.49</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>524.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>82.66</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>495.325</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>497.3</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>497.15</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>497.07</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>497.3833333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>496.7142857142857</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>496.5875</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>498.3277777777778</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>497.465</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>132.944986272518</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>122.7146147232133</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>116.0063683596724</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>107.4652739260455</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>99.24625797591676</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>95.75312644759855</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>94.15607969616195</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>92.7071752320508</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>92.92221895219679</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>312</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>312</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>312</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>312</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>312</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>312</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>312</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>312</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>312</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>679</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>679</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>679</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>679</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>679</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>679</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>679</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>679</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>679</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.8823529411764706</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.85</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.85</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>517</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>83.01000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>521</v>
       </c>
       <c r="C20" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D20" t="n">
         <v>58</v>
-      </c>
-      <c r="D20" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E20" t="n">
         <v>521</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>503.6043931910016</v>
-      </c>
-      <c r="J20" t="n">
-        <v>79.08146794990625</v>
-      </c>
-      <c r="K20" t="n">
-        <v>514.8850972461704</v>
-      </c>
-      <c r="L20" t="n">
-        <v>72.45510023060775</v>
-      </c>
-      <c r="M20" t="n">
-        <v>505.5757335518613</v>
-      </c>
-      <c r="N20" t="n">
-        <v>66.25411629556828</v>
-      </c>
-      <c r="O20" t="n">
-        <v>505.9278625506065</v>
-      </c>
-      <c r="P20" t="n">
-        <v>80.39278702722501</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>502.5021226510813</v>
-      </c>
       <c r="R20" t="n">
-        <v>75.68723372656969</v>
+        <v>503.6</v>
       </c>
       <c r="S20" t="n">
-        <v>508.2796073939799</v>
+        <v>79.08</v>
       </c>
       <c r="T20" t="n">
-        <v>76.0163829197423</v>
+        <v>514.89</v>
       </c>
       <c r="U20" t="n">
-        <v>511.0155003947905</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>75.89219373948661</v>
+        <v>505.58</v>
       </c>
       <c r="W20" t="n">
-        <v>512.8328114408988</v>
+        <v>66.25</v>
       </c>
       <c r="X20" t="n">
-        <v>78.5596312824572</v>
+        <v>505.93</v>
       </c>
       <c r="Y20" t="n">
-        <v>509.927803827122</v>
+        <v>80.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>83.69578682371809</v>
+        <v>502.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>75.69</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>508.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>76.02</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>511.02</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>75.89</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>512.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>78.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>509.93</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>83.7</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>503.8</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>502.1666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>501.6</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>501.46</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>502.025</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>502.9</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>501.91875</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>500.7277777777778</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>500.24</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>107.1063023355769</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>94.72524596020969</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>87.4693660660691</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>96.79777063548518</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>93.88516589429877</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>89.92141807473583</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>88.52894808161622</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>87.62564506375691</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>91.11488572126949</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>363</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>363</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>363</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>355</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>355</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>355</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>355</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>355</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>352</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7142857142857143</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>509.93</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>83.7</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>522</v>
       </c>
       <c r="C21" t="n">
+        <v>85.9896219421794</v>
+      </c>
+      <c r="D21" t="n">
         <v>58</v>
-      </c>
-      <c r="D21" t="n">
-        <v>85.9896219421794</v>
       </c>
       <c r="E21" t="n">
         <v>522</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>74.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>561.9464126731026</v>
-      </c>
-      <c r="J21" t="n">
-        <v>57.92307033780186</v>
-      </c>
-      <c r="K21" t="n">
-        <v>537.2047683527229</v>
-      </c>
-      <c r="L21" t="n">
-        <v>65.6301253820875</v>
-      </c>
-      <c r="M21" t="n">
-        <v>536.5406991514157</v>
-      </c>
-      <c r="N21" t="n">
-        <v>56.96950609629592</v>
-      </c>
-      <c r="O21" t="n">
-        <v>531.9160658666628</v>
-      </c>
-      <c r="P21" t="n">
-        <v>57.83612135740653</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>533.8809395909922</v>
-      </c>
       <c r="R21" t="n">
-        <v>53.46355721922222</v>
+        <v>561.95</v>
       </c>
       <c r="S21" t="n">
-        <v>527.3528681316619</v>
+        <v>57.92</v>
       </c>
       <c r="T21" t="n">
-        <v>60.21432920649301</v>
+        <v>537.2</v>
       </c>
       <c r="U21" t="n">
-        <v>522.3385421066862</v>
+        <v>65.63</v>
       </c>
       <c r="V21" t="n">
-        <v>63.12032647990644</v>
+        <v>536.54</v>
       </c>
       <c r="W21" t="n">
-        <v>522.6037970605306</v>
+        <v>56.97</v>
       </c>
       <c r="X21" t="n">
-        <v>62.443748467729</v>
+        <v>531.92</v>
       </c>
       <c r="Y21" t="n">
-        <v>526.8101147369056</v>
+        <v>57.84</v>
       </c>
       <c r="Z21" t="n">
-        <v>67.35778768537713</v>
+        <v>533.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>53.46</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>527.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>60.21</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>522.34</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>63.12</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>522.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>62.44</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>526.8099999999999</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>67.36</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>495.4</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>496.95</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>497.5</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>499.15</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>497.9666666666666</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>498.2714285714285</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>498.125</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>497.7166666666666</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>497.825</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>83.28799433291691</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>82.03788250964713</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>76.59552859012072</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>74.01045534247172</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>72.92301115255428</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>71.867421872018</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>72.24634506326254</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>72.70666139433932</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>72.35187886295698</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>330</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>330</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>330</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>330</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>330</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>330</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>330</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>330</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>330</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>637</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>637</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>637</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>637</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>637</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>637</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>637</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>637</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>637</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>1</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>1</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>1</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.72</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>526.8099999999999</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>67.36</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>519.8</v>
       </c>
       <c r="C22" t="n">
+        <v>88.36174944403261</v>
+      </c>
+      <c r="D22" t="n">
         <v>59.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>88.36174944403261</v>
       </c>
       <c r="E22" t="n">
         <v>519.8</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>77.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7555</v>
+      </c>
       <c r="I22" t="n">
-        <v>520.3145038656687</v>
+        <v>2.855</v>
       </c>
       <c r="J22" t="n">
-        <v>64.45235787442304</v>
+        <v>2.9145</v>
       </c>
       <c r="K22" t="n">
-        <v>521.9301645369826</v>
+        <v>2.938</v>
       </c>
       <c r="L22" t="n">
-        <v>70.35421226555994</v>
+        <v>2.955</v>
       </c>
       <c r="M22" t="n">
-        <v>523.9871564591821</v>
+        <v>2.9615</v>
       </c>
       <c r="N22" t="n">
-        <v>71.19804608745345</v>
+        <v>2.3645</v>
       </c>
       <c r="O22" t="n">
-        <v>522.7276599645081</v>
+        <v>2.507</v>
       </c>
       <c r="P22" t="n">
-        <v>71.58295009956259</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>521.1847604074003</v>
-      </c>
+        <v>2.636</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>71.97575009996369</v>
+        <v>520.3140000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>521.0053543383412</v>
+        <v>64.452</v>
       </c>
       <c r="T22" t="n">
-        <v>73.155408264164</v>
+        <v>521.9305000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>520.1525571792467</v>
+        <v>70.35550000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>72.19250584993412</v>
+        <v>523.9870000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>520.1122398765818</v>
+        <v>71.19799999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>72.00198258505567</v>
+        <v>522.728</v>
       </c>
       <c r="Y22" t="n">
-        <v>518.9696476969855</v>
+        <v>71.58349999999999</v>
       </c>
       <c r="Z22" t="n">
-        <v>72.54465539597639</v>
+        <v>521.1835</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>71.97499999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>521.0055000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>73.15650000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>520.152</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>72.19199999999999</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>520.1125</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>72.001</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>518.97</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>72.54649999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>498.83875</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.0516666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>498.5693749999999</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>498.8369999999999</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.052</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>498.57</v>
+      </c>
+      <c r="AV22" t="n">
         <v>498.7299999999999</v>
       </c>
-      <c r="AN22" t="n">
-        <v>498.7683333333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.0907142857142</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.1537499999999</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.2261111111112</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.1295</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>93.65228316191053</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>88.61750029430064</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>86.49864352407731</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>85.9197119573162</v>
-      </c>
       <c r="AW22" t="n">
-        <v>84.28132165736852</v>
+        <v>498.7689999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>84.74236075407012</v>
+        <v>499.0905</v>
       </c>
       <c r="AY22" t="n">
-        <v>84.50093392678869</v>
+        <v>499.1545</v>
       </c>
       <c r="AZ22" t="n">
-        <v>84.69776208014264</v>
+        <v>499.2275</v>
       </c>
       <c r="BA22" t="n">
-        <v>84.95766586037713</v>
+        <v>499.1294999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>93.65299999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>88.61800000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>86.49949999999998</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>85.9195</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>84.28150000000002</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>84.742</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>84.5005</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>84.699</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>84.95699999999999</v>
+      </c>
+      <c r="BK22" t="n">
         <v>340.05</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>339.2</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>339.2</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>338.75</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>337.85</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>334.85</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>334.65</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>333.6</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>333.3</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>659.3</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>659.75</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>659.95</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6590659340659342</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6601495434390171</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7238426477203568</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.80480462691763</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.8335157579778322</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.8517548727576996</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.8473534215182822</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.8412356492122093</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8064784184753033</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>518.97</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>72.54649999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.542383664469075</v>
       </c>
       <c r="C23" t="n">
+        <v>2.326827414887755</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.569445091341791</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.326827414887755</v>
       </c>
       <c r="E23" t="n">
         <v>1.542383664469075</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03548906429043356</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.229034708944167</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2665071342977124</v>
+      </c>
       <c r="I23" t="n">
-        <v>30.39575885918516</v>
+        <v>0.2622072302186714</v>
       </c>
       <c r="J23" t="n">
-        <v>23.54203786123676</v>
+        <v>0.2334517869756093</v>
       </c>
       <c r="K23" t="n">
-        <v>16.48338008926074</v>
+        <v>0.2191034362794744</v>
       </c>
       <c r="L23" t="n">
-        <v>17.92849409942145</v>
+        <v>0.2287379562547042</v>
       </c>
       <c r="M23" t="n">
-        <v>14.96560582936038</v>
+        <v>0.2129560122605011</v>
       </c>
       <c r="N23" t="n">
-        <v>16.50314641130418</v>
+        <v>0.3695868959855186</v>
       </c>
       <c r="O23" t="n">
-        <v>13.47369543585876</v>
+        <v>0.3526754882324543</v>
       </c>
       <c r="P23" t="n">
-        <v>14.57646832203439</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>11.36018763679505</v>
-      </c>
+        <v>0.323523366112948</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>13.65202738276483</v>
+        <v>30.39611252844853</v>
       </c>
       <c r="S23" t="n">
-        <v>9.277034725137083</v>
+        <v>23.54157165079413</v>
       </c>
       <c r="T23" t="n">
-        <v>14.48232941005935</v>
+        <v>16.48361434401161</v>
       </c>
       <c r="U23" t="n">
-        <v>10.29779967360454</v>
+        <v>17.92790664240941</v>
       </c>
       <c r="V23" t="n">
-        <v>12.42138351877906</v>
+        <v>14.96527422507116</v>
       </c>
       <c r="W23" t="n">
-        <v>10.21674055235687</v>
+        <v>16.50343396483226</v>
       </c>
       <c r="X23" t="n">
-        <v>11.15529472795174</v>
+        <v>13.47348179124265</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.22451998766743</v>
+        <v>14.57609660946376</v>
       </c>
       <c r="Z23" t="n">
-        <v>10.96630367918936</v>
+        <v>11.36027671781209</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>13.65234990376151</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>9.277252017704383</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>14.48292398327296</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>10.29804355460937</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>12.41993202795198</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>10.21649691481998</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>11.15501298685224</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>10.22406294766883</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>10.96623347275387</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.654903654500929</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.278098750741194</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.961322035844569</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.655232874718256</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.27871986223106</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.96154879730547</v>
+      </c>
+      <c r="AV23" t="n">
         <v>2.393090932356372</v>
       </c>
-      <c r="AN23" t="n">
-        <v>2.065001097375919</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.963106412907761</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.92706271918799</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.585563833645725</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.38384941757633</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>24.9687109949386</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>19.64667888338823</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>16.63150658371983</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.68508031192021</v>
-      </c>
       <c r="AW23" t="n">
-        <v>13.82465248523038</v>
+        <v>2.063815832256765</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.70072386235573</v>
+        <v>1.96341666489821</v>
       </c>
       <c r="AY23" t="n">
-        <v>12.48728339469658</v>
+        <v>1.927767934821595</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12.09991031379214</v>
+        <v>1.585121197425083</v>
       </c>
       <c r="BA23" t="n">
-        <v>11.44027760320652</v>
+        <v>1.385813365576531</v>
       </c>
       <c r="BB23" t="n">
+        <v>24.96822066463477</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19.6467154346069</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>16.63092125656619</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>15.68647874847366</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>13.82548191793537</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>12.69947723747962</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>12.48775968066752</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>12.09955366727915</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>11.43875595922637</v>
+      </c>
+      <c r="BK23" t="n">
         <v>31.3729266456891</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>30.77182580150054</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>30.77182580150054</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>30.45942080522008</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>29.18773174144449</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>25.90524230628559</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>25.8054971703807</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>25.35723710667648</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>25.2380247788301</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>29.88416232546492</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>28.80218376223727</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>28.35391925011611</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3247050164989665</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2619218437957812</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1419770301370424</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1374816458140506</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.1196713464664896</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1211858680621065</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1271624326585158</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1172054453415057</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1086953997576922</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>10.22406294766883</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>10.96623347275387</v>
       </c>
     </row>
   </sheetData>
